--- a/input/mapping/043. OCB_GOLD_TCKH_T24_CRB_PHAT.xlsx
+++ b/input/mapping/043. OCB_GOLD_TCKH_T24_CRB_PHAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/01. KHTC - Phân tích/06. Mapping View Layer 1/01.REVIEWED__OK/MAPPING_GOLD_BATCH_01_20260714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1219" documentId="13_ncr:1_{41AF731F-2010-41DC-BF12-24D975B98159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{026DE5F6-9F48-4484-9C05-F47C805D0757}"/>
+  <xr:revisionPtr revIDLastSave="1230" documentId="13_ncr:1_{41AF731F-2010-41DC-BF12-24D975B98159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30ED58E8-ABB4-45DE-8760-FFFDEB56DFE9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="9" r:id="rId1"/>
@@ -127,48 +127,17 @@
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS T24_CRB (
-    MONTH_DAY       DECIMAL(4, 0),
-    DATA_DATE       DECIMAL(8, 0),
-    NGAY            STRING,
-    CHINHANH        STRING,
-    NGOAITE         STRING,
-    GL              STRING,
-    TIEUKHOAN       STRING,
-    TEN             STRING,
-    NGOAITE1        DECIMAL(20, 4),
-    NOITE           DECIMAL(20, 4),
-    SOTKCU          STRING,
-    LAISUAT         STRING,
-    KYHAN           STRING,
-    STARTDATE       STRING,
-    ENDDATE         STRING,
-    MASP            STRING,
-    LAIDATRA        STRING,
-    LOANCLASS       STRING,
-    CIF             DECIMAL(18, 0),
-    CATEGORY        DECIMAL(6, 0)
-)
-USING DELTA;
--- -------------------------------------------------------
--- STEP 1: Xóa dữ liệu cũ theo ngày
--- -------------------------------------------------------
 DELETE FROM T24_CRB
-WHERE DATA_DATE = CAST(:DATADT AS DECIMAL(8, 0));
--- -------------------------------------------------------
--- STEP 2: Nạp dữ liệu mới từ Raw Vault
--- -------------------------------------------------------
+WHERE DATA_DATE = CAST(:target_date AS DECIMAL(8, 0));
 INSERT INTO T24_CRB
 WITH
--- STS HUB: chỉ giữ key có trạng thái MỚI NHẤT (&lt;= :DATADT) = 'D'
 crb_sts_del AS (
     SELECT crb_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_crb')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY crb_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
--- HUB active: hub CRB đã LOẠI key bị xóa (anti-join crb_sts_del)
 crb_active AS (
     SELECT
         h.crb_hashkey,
@@ -177,11 +146,10 @@
         h.source_event_date
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_crb') h
     LEFT JOIN crb_sts_del d ON d.crb_hashkey = h.crb_hashkey
-    WHERE h.source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE h.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
       AND d.crb_hashkey IS NULL
       AND h.tieukhoan != 'TOTAL'
 ),
--- MUL SAT: thông tin CRB — bản hiệu lực mới nhất &lt;= :DATADT, mỗi (crb_hashkey, ma_key)
 crb_info AS (
     SELECT
         crb_hashkey,
@@ -196,10 +164,9 @@
         max_by(loanclass, source_event_date) AS loanclass,
         max_by(ten,       source_event_date) AS ten
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_crb_information')
-    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date = TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY crb_hashkey, ma_key
 ),
--- MUL SAT: số dư CRB — bản hiệu lực mới nhất &lt;= :DATADT, mỗi (crb_hashkey, ma_key)
 crb_balance AS (
     SELECT
         crb_hashkey,
@@ -209,16 +176,15 @@
         max_by(noite,    source_event_date) AS noite,
         max_by(category, source_event_date) AS category
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance')
-    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date = TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY crb_hashkey, ma_key
 ),
--- LINK: CHINHANH — link_crb_branch (con trỏ mới nhất &lt;= :DATADT) → hub_branch.business_key
 crb_branch_cur AS (
     SELECT
         crb_hashkey,
         max_by(branch_hashkey, source_event_date) AS branch_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_crb_branch')
-    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY crb_hashkey
 ),
 crb_branch AS (
@@ -229,13 +195,12 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_branch') hb
         ON l.branch_hashkey = hb.branch_hashkey
 ),
--- LINK: CIF — link_crb_customer (con trỏ mới nhất &lt;= :DATADT) → hub_customer.business_key
 crb_customer_cur AS (
     SELECT
         crb_hashkey,
         max_by(customer_hashkey, source_event_date) AS customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_crb_customer')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY crb_hashkey
 ),
 crb_customer AS (
@@ -247,45 +212,25 @@
         ON l.customer_hashkey = hc.customer_hashkey
 )
 SELECT
-    -- STT 1 | MONTH_DAY | DECIMAL(4,0) | transform: Right(DATADT, 4) → lấy MMDD
-    CAST(RIGHT(:DATADT, 4) AS DECIMAL(4, 0))                       AS MONTH_DAY,
-    -- STT 2 | DATA_DATE | DECIMAL(8,0) | transform: DATADT dạng yyyyMMdd
-    CAST(:DATADT AS DECIMAL(8, 0))                                 AS DATA_DATE,
-    -- STT 3 | NGAY | STRING | transform: = DATADT (yyyyMMdd)
-    :DATADT                                                        AS NGAY,
-    -- STT 4 | CHINHANH | link_crb_branch → hub_branch.business_key + bỏ newline
+    CAST(RIGHT(:target_date, 4) AS DECIMAL(4, 0))                       AS MONTH_DAY,
+    CAST(:target_date AS DECIMAL(8, 0))                                 AS DATA_DATE,
+    :target_date                                                        AS NGAY,
     REGEXP_REPLACE(cb.chinhanh, '[\r\n]', '')                      AS CHINHANH,
-    -- STT 5 | NGOAITE | sat_crb_balance
     sb.ngoaite                                                     AS NGOAITE,
-    -- STT 6 | GL | hub_crb.gl
     hub.gl                                                         AS GL,
-    -- STT 7 | TIEUKHOAN | hub_crb.tieukhoan
     hub.tieukhoan                                                  AS TIEUKHOAN,
-    -- STT 8 | TEN | sat_crb_information
     si.ten                                                         AS TEN,
-    -- STT 9 | NGOAITE1 | sat_crb_balance
     sb.ngoaite1                                                    AS NGOAITE1,
-    -- STT 10 | NOITE | sat_crb_balance
     sb.noite                                                       AS NOITE,
-    -- STT 11 | SOTKCU | sat_crb_information
     si.sotkcu                                                      AS SOTKCU,
-    -- STT 12 | LAISUAT | sat_crb_information
     si.laisuat                                                     AS LAISUAT,
-    -- STT 13 | KYHAN | sat_crb_information
     si.kyhan                                                       AS KYHAN,
-    -- STT 14 | STARTDATE | sat_crb_information
     si.startdate                                                   AS STARTDATE,
-    -- STT 15 | ENDDATE | transform: IF ENDDATE = 0 THEN NULL
     NULLIF(si.enddate, 0)                                          AS ENDDATE,
-    -- STT 16 | MASP | sat_crb_information
     si.masp                                                        AS MASP,
-    -- STT 17 | LAIDATRA | sat_crb_information
     si.laidatra                                                    AS LAIDATRA,
-    -- STT 18 | LOANCLASS | sat_crb_information
     si.loanclass                                                   AS LOANCLASS,
-    -- STT 19 | CIF | link_crb_customer → hub_customer.business_key
     cc.cif                                                         AS CIF,
-    -- STT 20 | CATEGORY | sat_crb_balance
     sb.category                                                    AS CATEGORY
 FROM crb_active hub
 LEFT JOIN crb_info si
@@ -1039,6 +984,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1050,15 +1004,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1409,59 +1354,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="6" customHeight="1"/>
     <row r="3" spans="1:10" ht="7.15" customHeight="1"/>
     <row r="4" spans="1:10" ht="19.899999999999999" customHeight="1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="F4" s="43" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="F4" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
     </row>
     <row r="5" spans="1:10" ht="19.899999999999999" customHeight="1">
-      <c r="A5" s="45"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
       <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="107.25" customHeight="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
       <c r="J6" s="11"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1"/>
@@ -1527,7 +1472,7 @@
   <cols>
     <col min="1" max="1" width="15.28515625" style="7" customWidth="1"/>
     <col min="2" max="2" width="22.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="219.5703125" style="7" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
@@ -1884,13 +1829,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="44"/>
       <c r="F1"/>
     </row>
     <row r="2" spans="1:6">
@@ -2007,14 +1952,14 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
